--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T19:21:03+00:00</t>
+    <t>2026-03-17T13:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T13:04:13+00:00</t>
+    <t>2026-03-18T17:17:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,7 +617,7 @@
     <t>ServiceRequest.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
+    <t>oid de la MPDH</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -627,9 +627,6 @@
   </si>
   <si>
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>https://identifiant-medicosocial-demandeorientation.esante.gouv.fr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1657,6 +1654,10 @@
   </si>
   <si>
     <t>demandeOrientation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-document-reference)
+</t>
   </si>
   <si>
     <t>Demande d'orientation</t>
@@ -4166,7 +4167,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>92</v>
@@ -4203,46 +4204,46 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="T16" t="s" s="2">
+      <c r="U16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4263,10 +4264,10 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
@@ -4277,10 +4278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4288,7 +4289,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>92</v>
@@ -4306,13 +4307,13 @@
         <v>161</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4326,43 +4327,43 @@
         <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4383,10 +4384,10 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -4397,10 +4398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4423,13 +4424,13 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4480,7 +4481,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4501,10 +4502,10 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4515,10 +4516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4541,16 +4542,16 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4600,7 +4601,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4621,10 +4622,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4635,10 +4636,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4661,16 +4662,16 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4720,7 +4721,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4738,13 +4739,13 @@
         <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4755,10 +4756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4784,13 +4785,13 @@
         <v>106</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4840,7 +4841,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4858,13 +4859,13 @@
         <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4875,14 +4876,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4901,13 +4902,13 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4958,7 +4959,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4976,13 +4977,13 @@
         <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4993,14 +4994,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5019,13 +5020,13 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5076,7 +5077,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5094,13 +5095,13 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5111,14 +5112,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5140,16 +5141,16 @@
         <v>150</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5198,7 +5199,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5216,13 +5217,13 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5233,10 +5234,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5262,13 +5263,13 @@
         <v>112</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5297,11 +5298,11 @@
         <v>177</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>269</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5318,7 +5319,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>92</v>
@@ -5336,27 +5337,27 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5382,13 +5383,13 @@
         <v>112</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5417,11 +5418,11 @@
         <v>177</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>280</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5438,7 +5439,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>92</v>
@@ -5456,16 +5457,16 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>135</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5473,10 +5474,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5502,16 +5503,16 @@
         <v>183</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5536,14 +5537,14 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5560,7 +5561,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5575,19 +5576,19 @@
         <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AN27" t="s" s="2">
-        <v>294</v>
-      </c>
       <c r="AO27" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5595,10 +5596,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5624,10 +5625,10 @@
         <v>112</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5635,7 +5636,7 @@
         <v>82</v>
       </c>
       <c r="Q28" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="R28" t="s" s="2">
         <v>82</v>
@@ -5659,11 +5660,11 @@
         <v>177</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>300</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5680,7 +5681,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5698,16 +5699,16 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5715,10 +5716,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5741,26 +5742,26 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="O29" t="s" s="2">
+      <c r="P29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q29" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="P29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q29" t="s" s="2">
-        <v>311</v>
-      </c>
       <c r="R29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5804,7 +5805,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5822,13 +5823,13 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5839,14 +5840,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5868,13 +5869,13 @@
         <v>183</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5900,14 +5901,14 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="Z30" t="s" s="2">
-        <v>320</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5924,7 +5925,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5939,34 +5940,34 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AO30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>326</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5988,13 +5989,13 @@
         <v>183</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6020,14 +6021,14 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="Z31" t="s" s="2">
-        <v>333</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6044,7 +6045,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6053,7 +6054,7 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>104</v>
@@ -6065,24 +6066,24 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6105,17 +6106,17 @@
         <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6164,7 +6165,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6185,10 +6186,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6199,10 +6200,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6225,13 +6226,13 @@
         <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6282,7 +6283,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>92</v>
@@ -6297,34 +6298,34 @@
         <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6343,13 +6344,13 @@
         <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6400,7 +6401,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6418,31 +6419,31 @@
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>361</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6461,13 +6462,13 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6506,7 +6507,7 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
@@ -6516,7 +6517,7 @@
         <v>170</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6534,33 +6535,33 @@
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AO35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>372</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C36" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="B36" t="s" s="2">
+      <c r="D36" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="D36" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6579,13 +6580,13 @@
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6636,7 +6637,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6654,27 +6655,27 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>372</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6789,10 +6790,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6909,10 +6910,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6935,16 +6936,16 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6994,31 +6995,31 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI39" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7029,10 +7030,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7055,69 +7056,69 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q40" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="R40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="R40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
@@ -7125,22 +7126,22 @@
         <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7151,10 +7152,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7177,13 +7178,13 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7210,14 +7211,14 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>405</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7234,7 +7235,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7258,25 +7259,25 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7295,13 +7296,13 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7352,7 +7353,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7370,31 +7371,31 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AO42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>416</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7413,16 +7414,16 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7472,7 +7473,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7490,31 +7491,31 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>427</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7536,13 +7537,13 @@
         <v>183</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7568,14 +7569,14 @@
         <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>434</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7592,7 +7593,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7610,16 +7611,16 @@
         <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7627,14 +7628,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7653,16 +7654,16 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7712,7 +7713,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7730,16 +7731,16 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AN45" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AO45" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7747,10 +7748,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7776,10 +7777,10 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7806,14 +7807,14 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7830,7 +7831,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7854,10 +7855,10 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7865,10 +7866,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7891,13 +7892,13 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7948,7 +7949,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7972,10 +7973,10 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7983,10 +7984,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8012,13 +8013,13 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8044,14 +8045,14 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>463</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8068,7 +8069,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8086,16 +8087,16 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8103,10 +8104,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8129,16 +8130,16 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8188,7 +8189,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8206,16 +8207,16 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AN49" t="s" s="2">
-        <v>475</v>
-      </c>
       <c r="AO49" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8223,10 +8224,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8249,13 +8250,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8306,7 +8307,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8324,13 +8325,13 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8341,14 +8342,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8367,16 +8368,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8414,7 +8415,7 @@
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
@@ -8424,7 +8425,7 @@
         <v>170</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8442,13 +8443,13 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8459,10 +8460,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8577,10 +8578,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8606,10 +8607,10 @@
         <v>138</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8695,13 +8696,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C54" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>82</v>
@@ -8711,25 +8712,25 @@
         <v>92</v>
       </c>
       <c r="G54" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K54" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="H54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K54" t="s" s="2">
+      <c r="L54" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8815,10 +8816,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8844,13 +8845,13 @@
         <v>161</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8900,16 +8901,16 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI55" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -8935,10 +8936,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8964,13 +8965,13 @@
         <v>106</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8999,28 +9000,28 @@
         <v>188</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="Z56" t="s" s="2">
+      <c r="AA56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9055,10 +9056,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9084,13 +9085,13 @@
         <v>150</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9140,7 +9141,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9175,10 +9176,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9204,13 +9205,13 @@
         <v>161</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9260,7 +9261,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9295,16 +9296,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C59" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="B59" t="s" s="2">
+      <c r="D59" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="D59" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9323,16 +9324,16 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>485</v>
+        <v>527</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>528</v>
       </c>
       <c r="M59" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9382,7 +9383,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9397,16 +9398,16 @@
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9420,7 +9421,7 @@
         <v>529</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9538,7 +9539,7 @@
         <v>530</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9564,10 +9565,10 @@
         <v>138</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9656,10 +9657,10 @@
         <v>531</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>82</v>
@@ -9681,13 +9682,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9920,10 +9921,10 @@
         <v>138</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10248,7 +10249,7 @@
         <v>550</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10274,13 +10275,13 @@
         <v>161</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10330,16 +10331,16 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI67" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10368,7 +10369,7 @@
         <v>551</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10394,13 +10395,13 @@
         <v>106</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10429,28 +10430,28 @@
         <v>188</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="Z68" t="s" s="2">
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10488,7 +10489,7 @@
         <v>552</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10514,13 +10515,13 @@
         <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10570,7 +10571,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10608,7 +10609,7 @@
         <v>553</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10634,13 +10635,13 @@
         <v>161</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10690,7 +10691,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10728,13 +10729,13 @@
         <v>554</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>555</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10753,16 +10754,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>485</v>
+        <v>527</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>556</v>
       </c>
       <c r="M71" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10812,7 +10813,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10830,13 +10831,13 @@
         <v>555</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10850,7 +10851,7 @@
         <v>557</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10968,7 +10969,7 @@
         <v>558</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10994,10 +10995,10 @@
         <v>138</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11086,10 +11087,10 @@
         <v>559</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>82</v>
@@ -11111,13 +11112,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11350,10 +11351,10 @@
         <v>138</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11678,7 +11679,7 @@
         <v>565</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11704,13 +11705,13 @@
         <v>161</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11760,16 +11761,16 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI79" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>104</v>
@@ -11798,7 +11799,7 @@
         <v>566</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11824,13 +11825,13 @@
         <v>106</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11859,28 +11860,28 @@
         <v>188</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="Z80" t="s" s="2">
+      <c r="AA80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11918,7 +11919,7 @@
         <v>567</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11944,13 +11945,13 @@
         <v>150</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12000,7 +12001,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12038,7 +12039,7 @@
         <v>568</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12064,13 +12065,13 @@
         <v>161</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12120,7 +12121,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12158,13 +12159,13 @@
         <v>569</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C83" t="s" s="2">
         <v>570</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12183,16 +12184,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>485</v>
+        <v>527</v>
       </c>
       <c r="L83" t="s" s="2">
         <v>571</v>
       </c>
       <c r="M83" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12242,7 +12243,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12260,13 +12261,13 @@
         <v>570</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12280,7 +12281,7 @@
         <v>572</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12398,7 +12399,7 @@
         <v>573</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12424,10 +12425,10 @@
         <v>138</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12516,10 +12517,10 @@
         <v>574</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>82</v>
@@ -12541,13 +12542,13 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12780,10 +12781,10 @@
         <v>138</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13108,7 +13109,7 @@
         <v>580</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13134,13 +13135,13 @@
         <v>161</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13190,16 +13191,16 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI91" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>104</v>
@@ -13228,7 +13229,7 @@
         <v>581</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13254,13 +13255,13 @@
         <v>106</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13289,28 +13290,28 @@
         <v>188</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="Z92" t="s" s="2">
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13348,7 +13349,7 @@
         <v>582</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13374,13 +13375,13 @@
         <v>150</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13430,7 +13431,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13468,7 +13469,7 @@
         <v>583</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13494,13 +13495,13 @@
         <v>161</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13550,7 +13551,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13588,13 +13589,13 @@
         <v>584</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>585</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13613,16 +13614,16 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>485</v>
+        <v>527</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>586</v>
       </c>
       <c r="M95" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13672,7 +13673,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13690,13 +13691,13 @@
         <v>585</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AM95" t="s" s="2">
+      <c r="AN95" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13710,7 +13711,7 @@
         <v>587</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13828,7 +13829,7 @@
         <v>588</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13854,10 +13855,10 @@
         <v>138</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13946,10 +13947,10 @@
         <v>589</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>82</v>
@@ -13971,13 +13972,13 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14210,10 +14211,10 @@
         <v>138</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14538,7 +14539,7 @@
         <v>595</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14564,13 +14565,13 @@
         <v>161</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14620,16 +14621,16 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI103" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>104</v>
@@ -14658,7 +14659,7 @@
         <v>596</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14684,13 +14685,13 @@
         <v>106</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14719,28 +14720,28 @@
         <v>188</v>
       </c>
       <c r="Y104" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z104" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="Z104" t="s" s="2">
+      <c r="AA104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14778,7 +14779,7 @@
         <v>597</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14804,13 +14805,13 @@
         <v>150</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14860,7 +14861,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14898,7 +14899,7 @@
         <v>598</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14924,13 +14925,13 @@
         <v>161</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14980,7 +14981,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15198,7 +15199,7 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Y108" t="s" s="2">
         <v>612</v>
@@ -15361,7 +15362,7 @@
         <v>619</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>620</v>
@@ -15479,7 +15480,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>625</v>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T17:17:44+00:00</t>
+    <t>2026-03-19T09:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4228" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4226" uniqueCount="631">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T09:35:09+00:00</t>
+    <t>2026-06-08T15:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -907,13 +907,7 @@
     <t>Used for filtering what service request are retrieved and displayed.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Classification of the requested service.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-category|4.0.1</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j394-type-demande-compensation-ms</t>
   </si>
   <si>
     <t>typeDemande</t>
@@ -999,10 +993,7 @@
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
   </si>
   <si>
-    <t>Codes for tests or services that can be carried out by a designated individual, organization or healthcare service.  For laboratory, LOINC is  (preferred)[http://build.fhir.org/terminologies.html#preferred].</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j395-nature-demande-compensation-ms</t>
   </si>
   <si>
     <t>natureDemande</t>
@@ -1037,6 +1028,9 @@
   </si>
   <si>
     <t>For information from the medical record intended to support the delivery of the requested services, use the `supportingInformation` element.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Codified order entry details which are based on order context.</t>
@@ -2327,7 +2321,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="160.17578125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="108.3203125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="70.07421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="86.6484375" customWidth="true" bestFit="true"/>
@@ -5537,13 +5531,11 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y27" s="2"/>
+      <c r="Z27" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5576,16 +5568,16 @@
         <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>282</v>
@@ -5596,10 +5588,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5625,10 +5617,10 @@
         <v>112</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5636,7 +5628,7 @@
         <v>82</v>
       </c>
       <c r="Q28" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="R28" t="s" s="2">
         <v>82</v>
@@ -5660,10 +5652,10 @@
         <v>177</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5681,7 +5673,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5699,16 +5691,16 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5716,10 +5708,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5742,26 +5734,26 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="P29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q29" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="O29" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="P29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q29" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="R29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5805,7 +5797,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5823,13 +5815,13 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5840,14 +5832,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5869,13 +5861,13 @@
         <v>183</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5901,13 +5893,11 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5925,7 +5915,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5940,34 +5930,34 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>325</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5989,13 +5979,13 @@
         <v>183</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6021,13 +6011,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>288</v>
+        <v>328</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -6045,7 +6035,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6054,7 +6044,7 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>104</v>
@@ -6066,24 +6056,24 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6106,17 +6096,17 @@
         <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6165,7 +6155,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6186,10 +6176,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6200,10 +6190,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6226,13 +6216,13 @@
         <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6283,7 +6273,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>92</v>
@@ -6298,34 +6288,34 @@
         <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>350</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6344,13 +6334,13 @@
         <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6401,7 +6391,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6419,31 +6409,31 @@
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>360</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6462,13 +6452,13 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6507,7 +6497,7 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
@@ -6517,7 +6507,7 @@
         <v>170</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6535,33 +6525,33 @@
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6583,10 +6573,10 @@
         <v>211</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6637,7 +6627,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6655,27 +6645,27 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6790,10 +6780,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6910,10 +6900,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6936,16 +6926,16 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6995,7 +6985,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7004,22 +6994,22 @@
         <v>92</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7030,10 +7020,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7056,23 +7046,23 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q40" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="R40" t="s" s="2">
         <v>82</v>
@@ -7117,7 +7107,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7126,22 +7116,22 @@
         <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7152,10 +7142,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7178,13 +7168,13 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7211,13 +7201,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>288</v>
+        <v>328</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7235,7 +7225,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7259,25 +7249,25 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7296,13 +7286,13 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7353,7 +7343,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7371,31 +7361,31 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>415</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7414,16 +7404,16 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7473,7 +7463,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7491,31 +7481,31 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>426</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7537,13 +7527,13 @@
         <v>183</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7569,13 +7559,13 @@
         <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>288</v>
+        <v>328</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -7593,7 +7583,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7611,16 +7601,16 @@
         <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7628,14 +7618,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7654,16 +7644,16 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7713,7 +7703,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7731,16 +7721,16 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>446</v>
-      </c>
       <c r="AO45" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7748,10 +7738,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7777,10 +7767,10 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7807,13 +7797,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>288</v>
+        <v>328</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7831,7 +7821,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7855,10 +7845,10 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7866,10 +7856,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7892,13 +7882,13 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7949,7 +7939,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7973,10 +7963,10 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7984,10 +7974,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8013,13 +8003,13 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8045,13 +8035,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>288</v>
+        <v>328</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8069,7 +8059,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8087,16 +8077,16 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8104,10 +8094,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8130,16 +8120,16 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8189,7 +8179,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8207,16 +8197,16 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>474</v>
-      </c>
       <c r="AO49" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8224,10 +8214,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8250,13 +8240,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8307,7 +8297,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8325,13 +8315,13 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8342,14 +8332,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8368,16 +8358,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8415,7 +8405,7 @@
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
@@ -8425,7 +8415,7 @@
         <v>170</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8443,13 +8433,13 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8460,10 +8450,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8578,10 +8568,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8607,10 +8597,10 @@
         <v>138</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8696,13 +8686,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>82</v>
@@ -8712,25 +8702,25 @@
         <v>92</v>
       </c>
       <c r="G54" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="H54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8816,10 +8806,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8845,13 +8835,13 @@
         <v>161</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8901,7 +8891,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8910,7 +8900,7 @@
         <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -8936,10 +8926,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8965,13 +8955,13 @@
         <v>106</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9000,28 +8990,28 @@
         <v>188</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9056,10 +9046,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9085,13 +9075,13 @@
         <v>150</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9141,7 +9131,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9176,10 +9166,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9205,13 +9195,13 @@
         <v>161</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9261,7 +9251,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9296,16 +9286,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9324,16 +9314,16 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9383,7 +9373,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9398,16 +9388,16 @@
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9418,10 +9408,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9536,10 +9526,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9565,10 +9555,10 @@
         <v>138</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9654,13 +9644,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>82</v>
@@ -9682,13 +9672,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9774,10 +9764,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9892,10 +9882,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9921,10 +9911,10 @@
         <v>138</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10010,10 +10000,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10039,13 +10029,13 @@
         <v>106</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10053,7 +10043,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>82</v>
@@ -10095,7 +10085,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>92</v>
@@ -10130,10 +10120,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10159,10 +10149,10 @@
         <v>183</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10174,7 +10164,7 @@
         <v>82</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>82</v>
@@ -10193,7 +10183,7 @@
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10211,7 +10201,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10246,10 +10236,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10275,13 +10265,13 @@
         <v>161</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10331,7 +10321,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10340,7 +10330,7 @@
         <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10366,10 +10356,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10395,13 +10385,13 @@
         <v>106</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10430,28 +10420,28 @@
         <v>188</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10486,10 +10476,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10515,13 +10505,13 @@
         <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10571,7 +10561,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10606,10 +10596,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10635,13 +10625,13 @@
         <v>161</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10691,7 +10681,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10726,16 +10716,16 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10754,16 +10744,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10813,7 +10803,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10828,16 +10818,16 @@
         <v>104</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10848,10 +10838,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10966,10 +10956,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10995,10 +10985,10 @@
         <v>138</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11084,13 +11074,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>82</v>
@@ -11112,13 +11102,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11204,10 +11194,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11322,10 +11312,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11351,10 +11341,10 @@
         <v>138</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11440,10 +11430,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11469,13 +11459,13 @@
         <v>106</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11483,7 +11473,7 @@
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>82</v>
@@ -11525,7 +11515,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>92</v>
@@ -11560,10 +11550,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11589,10 +11579,10 @@
         <v>183</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11604,7 +11594,7 @@
         <v>82</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>82</v>
@@ -11623,7 +11613,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11641,7 +11631,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11676,10 +11666,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11705,13 +11695,13 @@
         <v>161</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11761,7 +11751,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11770,7 +11760,7 @@
         <v>92</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>104</v>
@@ -11796,10 +11786,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11825,13 +11815,13 @@
         <v>106</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11860,28 +11850,28 @@
         <v>188</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11916,10 +11906,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11945,13 +11935,13 @@
         <v>150</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12001,7 +11991,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12036,10 +12026,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12065,13 +12055,13 @@
         <v>161</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12121,7 +12111,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12156,16 +12146,16 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12184,16 +12174,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12243,7 +12233,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12258,16 +12248,16 @@
         <v>104</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12278,10 +12268,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12396,10 +12386,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12425,10 +12415,10 @@
         <v>138</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12514,13 +12504,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>82</v>
@@ -12542,13 +12532,13 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12634,10 +12624,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12752,10 +12742,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12781,10 +12771,10 @@
         <v>138</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12870,10 +12860,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12899,13 +12889,13 @@
         <v>106</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12913,7 +12903,7 @@
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>82</v>
@@ -12955,7 +12945,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>92</v>
@@ -12990,10 +12980,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13019,10 +13009,10 @@
         <v>183</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13034,7 +13024,7 @@
         <v>82</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>82</v>
@@ -13053,7 +13043,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13071,7 +13061,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13106,10 +13096,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13135,13 +13125,13 @@
         <v>161</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13191,7 +13181,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13200,7 +13190,7 @@
         <v>92</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>104</v>
@@ -13226,10 +13216,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13255,13 +13245,13 @@
         <v>106</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13290,28 +13280,28 @@
         <v>188</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13346,10 +13336,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13375,13 +13365,13 @@
         <v>150</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13431,7 +13421,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13466,10 +13456,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13495,13 +13485,13 @@
         <v>161</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13551,7 +13541,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13586,16 +13576,16 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13614,16 +13604,16 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13673,7 +13663,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13688,16 +13678,16 @@
         <v>104</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13708,10 +13698,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13826,10 +13816,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13855,10 +13845,10 @@
         <v>138</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13944,13 +13934,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>82</v>
@@ -13972,13 +13962,13 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14064,10 +14054,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14182,10 +14172,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14211,10 +14201,10 @@
         <v>138</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14300,10 +14290,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14329,13 +14319,13 @@
         <v>106</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14343,7 +14333,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14385,7 +14375,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>92</v>
@@ -14420,10 +14410,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14449,10 +14439,10 @@
         <v>183</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14464,7 +14454,7 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>82</v>
@@ -14483,7 +14473,7 @@
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14501,7 +14491,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14536,10 +14526,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14565,13 +14555,13 @@
         <v>161</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14621,7 +14611,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14630,7 +14620,7 @@
         <v>92</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>104</v>
@@ -14656,10 +14646,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14685,13 +14675,13 @@
         <v>106</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14720,28 +14710,28 @@
         <v>188</v>
       </c>
       <c r="Y104" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14776,10 +14766,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14805,13 +14795,13 @@
         <v>150</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14861,7 +14851,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14896,10 +14886,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14925,13 +14915,13 @@
         <v>161</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N106" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14981,7 +14971,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15016,10 +15006,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15042,16 +15032,16 @@
         <v>93</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15101,7 +15091,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15122,10 +15112,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15136,14 +15126,14 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15165,16 +15155,16 @@
         <v>183</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15199,13 +15189,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>288</v>
+        <v>328</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15223,7 +15213,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15244,24 +15234,24 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15284,13 +15274,13 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15341,7 +15331,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15359,27 +15349,27 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP109" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>621</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15405,10 +15395,10 @@
         <v>161</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15459,7 +15449,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15480,10 +15470,10 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15494,10 +15484,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15520,16 +15510,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15579,7 +15569,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15597,13 +15587,13 @@
         <v>82</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>135</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T15:24:46+00:00</t>
+    <t>2026-06-09T07:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T07:55:39+00:00</t>
+    <t>2026-06-09T09:58:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T09:58:53+00:00</t>
+    <t>2026-06-10T14:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4226" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4264" uniqueCount="642">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T14:13:27+00:00</t>
+    <t>2026-06-12T15:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -494,6 +494,13 @@
     <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 v2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 v2).  For further discussion and examples see the resource notes section below.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:type}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>idDemandeOrientation</t>
   </si>
   <si>
@@ -510,6 +517,12 @@
   </si>
   <si>
     <t>ClinicalStatement.identifier</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idDemandeOrientation</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idDemandeOrientation.id</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.id</t>
@@ -531,6 +544,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>ServiceRequest.identifier:idDemandeOrientation.extension</t>
+  </si>
+  <si>
     <t>ServiceRequest.identifier.extension</t>
   </si>
   <si>
@@ -544,12 +560,12 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
+    <t>ServiceRequest.identifier:idDemandeOrientation.use</t>
+  </si>
+  <si>
     <t>ServiceRequest.identifier.use</t>
   </si>
   <si>
@@ -578,6 +594,9 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idDemandeOrientation.type</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.type</t>
@@ -599,6 +618,14 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-service-request-identifier"/&gt;
+    &lt;code value="DEMANDE_ORIENTATION"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -614,6 +641,9 @@
     <t>CX.5</t>
   </si>
   <si>
+    <t>ServiceRequest.identifier:idDemandeOrientation.system</t>
+  </si>
+  <si>
     <t>ServiceRequest.identifier.system</t>
   </si>
   <si>
@@ -641,6 +671,9 @@
     <t>II.root or Role.id.root</t>
   </si>
   <si>
+    <t>ServiceRequest.identifier:idDemandeOrientation.value</t>
+  </si>
+  <si>
     <t>ServiceRequest.identifier.value</t>
   </si>
   <si>
@@ -663,6 +696,9 @@
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idDemandeOrientation.period</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.period</t>
@@ -685,6 +721,9 @@
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:idDemandeOrientation.assigner</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.assigner</t>
@@ -2294,12 +2333,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP111"/>
+  <dimension ref="A1:AP112"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="75.44140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.4765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.2421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.8359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3562,7 +3601,7 @@
         <v>92</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>82</v>
@@ -3621,16 +3660,14 @@
         <v>82</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>149</v>
@@ -3648,38 +3685,40 @@
         <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>92</v>
@@ -3691,18 +3730,20 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3751,56 +3792,56 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
@@ -3812,17 +3853,15 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>141</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3859,43 +3898,43 @@
         <v>82</v>
       </c>
       <c r="AB13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC13" t="s" s="2">
+      <c r="AG13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3906,46 +3945,44 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3969,43 +4006,43 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>82</v>
@@ -4014,10 +4051,10 @@
         <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>82</v>
@@ -4028,10 +4065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4048,25 +4085,25 @@
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4091,13 +4128,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -4115,7 +4152,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4136,10 +4173,10 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>192</v>
+        <v>135</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>82</v>
@@ -4150,10 +4187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4176,19 +4213,19 @@
         <v>93</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4198,46 +4235,46 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="T16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4258,10 +4295,10 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
@@ -4272,10 +4309,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4298,18 +4335,20 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
@@ -4395,7 +4434,7 @@
         <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4403,7 +4442,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>92</v>
@@ -4418,7 +4457,7 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>212</v>
@@ -4426,7 +4465,9 @@
       <c r="M18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="N18" s="2"/>
+      <c r="N18" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4439,7 +4480,7 @@
         <v>82</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>82</v>
@@ -4475,7 +4516,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4496,10 +4537,10 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4510,10 +4551,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4536,17 +4577,15 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4595,7 +4634,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4616,10 +4655,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4630,10 +4669,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4644,7 +4683,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -4656,16 +4695,16 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4715,13 +4754,13 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
@@ -4733,13 +4772,13 @@
         <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4750,10 +4789,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4776,16 +4815,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>106</v>
+        <v>237</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4835,7 +4874,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4853,13 +4892,13 @@
         <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4870,14 +4909,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4896,15 +4935,17 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>240</v>
+        <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4953,7 +4994,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4971,13 +5012,13 @@
         <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4988,14 +5029,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5014,13 +5055,13 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5071,7 +5112,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5089,13 +5130,13 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5106,21 +5147,21 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -5132,20 +5173,16 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>150</v>
+        <v>259</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5193,13 +5230,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -5211,13 +5248,13 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5228,18 +5265,18 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>92</v>
@@ -5248,24 +5285,26 @@
         <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5289,13 +5328,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5313,10 +5352,10 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>92</v>
@@ -5331,19 +5370,19 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>272</v>
+        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
@@ -5409,7 +5448,7 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="Y26" t="s" s="2">
         <v>278</v>
@@ -5454,24 +5493,24 @@
         <v>280</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>135</v>
+        <v>281</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5479,7 +5518,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>92</v>
@@ -5488,26 +5527,24 @@
         <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5531,11 +5568,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5553,13 +5592,13 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5568,19 +5607,19 @@
         <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>290</v>
+        <v>135</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5588,10 +5627,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5614,72 +5653,72 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M28" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y28" s="2"/>
+      <c r="Z28" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q28" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="R28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
@@ -5688,19 +5727,19 @@
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5708,10 +5747,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5728,13 +5767,13 @@
         <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>304</v>
@@ -5742,45 +5781,41 @@
       <c r="M29" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q29" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="O29" t="s" s="2">
+      <c r="R29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y29" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="P29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q29" t="s" s="2">
+      <c r="Z29" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="R29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5797,7 +5832,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5818,13 +5853,13 @@
         <v>309</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5832,14 +5867,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5852,70 +5887,76 @@
         <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>183</v>
+        <v>314</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="P30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q30" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="R30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="O30" s="2"/>
-      <c r="P30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q30" s="2"/>
-      <c r="R30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y30" s="2"/>
-      <c r="Z30" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5930,41 +5971,41 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>321</v>
+        <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5976,16 +6017,16 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6011,13 +6052,11 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -6035,56 +6074,56 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AN31" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP31" t="s" s="2">
-        <v>322</v>
+        <v>333</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -6096,18 +6135,18 @@
         <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>334</v>
+        <v>189</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
         <v>337</v>
       </c>
+      <c r="N32" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6131,13 +6170,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -6155,16 +6194,16 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>104</v>
@@ -6176,24 +6215,24 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6201,7 +6240,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>92</v>
@@ -6216,16 +6255,18 @@
         <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6273,10 +6314,10 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>92</v>
@@ -6288,38 +6329,38 @@
         <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AN33" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>92</v>
@@ -6391,10 +6432,10 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>92</v>
@@ -6406,34 +6447,34 @@
         <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6452,13 +6493,13 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6497,17 +6538,19 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AC35" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6545,13 +6588,11 @@
         <v>370</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C36" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="D36" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6570,13 +6611,13 @@
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>211</v>
+        <v>372</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6615,19 +6656,17 @@
         <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="AC36" s="2"/>
       <c r="AD36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6645,31 +6684,33 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>369</v>
+        <v>380</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="D37" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6685,16 +6726,16 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>161</v>
+        <v>221</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>162</v>
+        <v>373</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6745,7 +6786,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>164</v>
+        <v>370</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6757,44 +6798,44 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>165</v>
+        <v>378</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6806,17 +6847,15 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="M38" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="N38" t="s" s="2">
-        <v>141</v>
-      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6853,43 +6892,43 @@
         <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC38" t="s" s="2">
+      <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6900,21 +6939,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6923,19 +6962,19 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>378</v>
+        <v>138</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>379</v>
+        <v>139</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>380</v>
+        <v>172</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>381</v>
+        <v>141</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6973,43 +7012,43 @@
         <v>82</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>382</v>
+        <v>175</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>386</v>
+        <v>169</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7046,24 +7085,22 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q40" t="s" s="2">
-        <v>392</v>
-      </c>
+      <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7116,22 +7153,22 @@
         <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7142,10 +7179,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7168,20 +7205,24 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q41" s="2"/>
+      <c r="Q41" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="R41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7201,13 +7242,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7225,7 +7266,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7234,40 +7275,40 @@
         <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>406</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7286,13 +7327,13 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>378</v>
+        <v>409</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7319,13 +7360,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7343,7 +7384,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7361,31 +7402,31 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7404,17 +7445,15 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>416</v>
+        <v>389</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N43" t="s" s="2">
         <v>419</v>
       </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7463,7 +7502,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7524,16 +7563,16 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>183</v>
+        <v>427</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7559,13 +7598,13 @@
         <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -7601,19 +7640,19 @@
         <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="45">
@@ -7632,7 +7671,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7644,16 +7683,16 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7679,13 +7718,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7709,7 +7748,7 @@
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
@@ -7721,16 +7760,16 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7738,14 +7777,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7764,15 +7803,17 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>183</v>
+        <v>449</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>451</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7797,13 +7838,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7821,7 +7862,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7839,16 +7880,16 @@
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>454</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7856,10 +7897,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7882,13 +7923,13 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>452</v>
+        <v>189</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7915,13 +7956,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7939,7 +7980,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7963,10 +8004,10 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7974,10 +8015,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8000,17 +8041,15 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>183</v>
+        <v>463</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8035,13 +8074,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>460</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8059,7 +8098,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8077,16 +8116,16 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>461</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>462</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8094,10 +8133,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8120,7 +8159,7 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>466</v>
+        <v>189</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>467</v>
@@ -8155,13 +8194,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>82</v>
+        <v>470</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8179,7 +8218,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8197,16 +8236,16 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8214,10 +8253,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8237,18 +8276,20 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8297,7 +8338,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8315,16 +8356,16 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>82</v>
+        <v>475</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8332,14 +8373,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8358,17 +8399,15 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8405,17 +8444,19 @@
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AC51" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8433,13 +8474,13 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8450,21 +8491,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8476,15 +8517,17 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>161</v>
+        <v>493</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>162</v>
+        <v>494</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8521,43 +8564,41 @@
         <v>82</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>164</v>
+        <v>491</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>165</v>
+        <v>500</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8568,10 +8609,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8579,10 +8620,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8594,13 +8635,13 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>492</v>
+        <v>166</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>493</v>
+        <v>167</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8639,43 +8680,43 @@
         <v>82</v>
       </c>
       <c r="AB53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC53" t="s" s="2">
+      <c r="AG53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8686,14 +8727,12 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8702,7 +8741,7 @@
         <v>92</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>496</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8714,13 +8753,13 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>497</v>
+        <v>138</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8759,19 +8798,19 @@
         <v>82</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8806,21 +8845,23 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="D55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>92</v>
+        <v>507</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8829,20 +8870,18 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>161</v>
+        <v>508</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8891,19 +8930,19 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>504</v>
+        <v>175</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8915,7 +8954,7 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8926,10 +8965,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8952,16 +8991,16 @@
         <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8987,13 +9026,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9011,7 +9050,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9020,7 +9059,7 @@
         <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>104</v>
@@ -9046,10 +9085,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9072,16 +9111,16 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9107,13 +9146,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9131,7 +9170,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9155,7 +9194,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9166,10 +9205,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9192,16 +9231,16 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9251,7 +9290,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9275,7 +9314,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9286,23 +9325,21 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9311,19 +9348,19 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>525</v>
+        <v>165</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>484</v>
+        <v>531</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>485</v>
+        <v>532</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9373,13 +9410,13 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>480</v>
+        <v>533</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
@@ -9388,16 +9425,16 @@
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>524</v>
+        <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>487</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>488</v>
+        <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>489</v>
+        <v>135</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9408,21 +9445,23 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9434,15 +9473,17 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>161</v>
+        <v>536</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>162</v>
+        <v>537</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9491,31 +9532,31 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>164</v>
+        <v>491</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>165</v>
+        <v>500</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9526,10 +9567,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9537,10 +9578,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9552,13 +9593,13 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>492</v>
+        <v>166</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>493</v>
+        <v>167</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9597,43 +9638,43 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC61" t="s" s="2">
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9644,14 +9685,12 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9660,7 +9699,7 @@
         <v>92</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9672,13 +9711,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>497</v>
+        <v>138</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9717,19 +9756,19 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9764,18 +9803,20 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="D63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>92</v>
@@ -9790,13 +9831,13 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>161</v>
+        <v>508</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>162</v>
+        <v>509</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>163</v>
+        <v>510</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9847,19 +9888,19 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -9871,7 +9912,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9882,10 +9923,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9896,7 +9937,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9908,13 +9949,13 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>492</v>
+        <v>166</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>493</v>
+        <v>167</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9953,43 +9994,43 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC64" t="s" s="2">
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10000,10 +10041,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10011,10 +10052,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -10026,24 +10067,22 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>82</v>
@@ -10073,31 +10112,31 @@
         <v>82</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>540</v>
+        <v>175</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10109,7 +10148,7 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10120,10 +10159,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10131,7 +10170,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>92</v>
@@ -10146,25 +10185,27 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>183</v>
+        <v>106</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>82</v>
@@ -10179,11 +10220,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z66" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10201,10 +10244,10 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>92</v>
@@ -10213,7 +10256,7 @@
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -10236,10 +10279,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>500</v>
+        <v>553</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10259,20 +10302,18 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>501</v>
+        <v>554</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10282,7 +10323,7 @@
         <v>82</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>82</v>
+        <v>556</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>82</v>
@@ -10297,13 +10338,11 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>557</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10321,7 +10360,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>504</v>
+        <v>558</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10330,7 +10369,7 @@
         <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10356,10 +10395,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10382,16 +10421,16 @@
         <v>93</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10417,13 +10456,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10441,7 +10480,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10450,7 +10489,7 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10476,10 +10515,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10502,16 +10541,16 @@
         <v>93</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10537,13 +10576,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10561,7 +10600,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10585,7 +10624,7 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10596,10 +10635,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>551</v>
+        <v>561</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10622,16 +10661,16 @@
         <v>93</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10681,7 +10720,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10705,7 +10744,7 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10716,16 +10755,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>553</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10741,19 +10778,19 @@
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>525</v>
+        <v>165</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>554</v>
+        <v>530</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>484</v>
+        <v>531</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>485</v>
+        <v>532</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10803,13 +10840,13 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>480</v>
+        <v>533</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
@@ -10818,16 +10855,16 @@
         <v>104</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>553</v>
+        <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>487</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>488</v>
+        <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>489</v>
+        <v>135</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10838,14 +10875,16 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C72" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>564</v>
+      </c>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10864,15 +10903,17 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>161</v>
+        <v>536</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>162</v>
+        <v>565</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10921,31 +10962,31 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>164</v>
+        <v>491</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>82</v>
+        <v>564</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>165</v>
+        <v>500</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10956,10 +10997,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10967,10 +11008,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -10982,13 +11023,13 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>492</v>
+        <v>166</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>493</v>
+        <v>167</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11027,43 +11068,43 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC73" t="s" s="2">
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11074,14 +11115,12 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C74" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11090,7 +11129,7 @@
         <v>92</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11102,13 +11141,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>497</v>
+        <v>138</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11147,19 +11186,19 @@
         <v>82</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11194,18 +11233,20 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="C75" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="D75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>92</v>
@@ -11220,13 +11261,13 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>161</v>
+        <v>508</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>162</v>
+        <v>509</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>163</v>
+        <v>510</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11277,19 +11318,19 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11301,7 +11342,7 @@
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11312,10 +11353,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11326,7 +11367,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11338,13 +11379,13 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>492</v>
+        <v>166</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>493</v>
+        <v>167</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11383,43 +11424,43 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC76" t="s" s="2">
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11430,10 +11471,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11441,10 +11482,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
@@ -11456,24 +11497,22 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>82</v>
@@ -11503,31 +11542,31 @@
         <v>82</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>540</v>
+        <v>175</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11539,7 +11578,7 @@
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11550,10 +11589,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11561,7 +11600,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>92</v>
@@ -11576,25 +11615,27 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>183</v>
+        <v>106</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>562</v>
+        <v>82</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>82</v>
@@ -11609,11 +11650,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y78" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z78" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11631,10 +11674,10 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>92</v>
@@ -11643,7 +11686,7 @@
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11666,10 +11709,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>500</v>
+        <v>553</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11689,20 +11732,18 @@
         <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>501</v>
+        <v>554</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11712,7 +11753,7 @@
         <v>82</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>82</v>
@@ -11727,13 +11768,11 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>82</v>
+        <v>557</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11751,7 +11790,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>504</v>
+        <v>558</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11760,7 +11799,7 @@
         <v>92</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>104</v>
@@ -11786,10 +11825,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11812,16 +11851,16 @@
         <v>93</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11847,13 +11886,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -11871,7 +11910,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11880,7 +11919,7 @@
         <v>92</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>104</v>
@@ -11906,10 +11945,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11932,16 +11971,16 @@
         <v>93</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11967,13 +12006,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -11991,7 +12030,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12015,7 +12054,7 @@
         <v>82</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12026,10 +12065,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12052,16 +12091,16 @@
         <v>93</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12111,7 +12150,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12135,7 +12174,7 @@
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12146,16 +12185,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>568</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12171,19 +12208,19 @@
         <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>525</v>
+        <v>165</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>569</v>
+        <v>530</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>484</v>
+        <v>531</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>485</v>
+        <v>532</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12233,13 +12270,13 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>480</v>
+        <v>533</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
@@ -12248,16 +12285,16 @@
         <v>104</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>568</v>
+        <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>487</v>
+        <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>488</v>
+        <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>489</v>
+        <v>135</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12268,14 +12305,16 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C84" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="D84" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12294,15 +12333,17 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>161</v>
+        <v>536</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>162</v>
+        <v>580</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12351,31 +12392,31 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>164</v>
+        <v>491</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>165</v>
+        <v>500</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12386,10 +12427,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12397,10 +12438,10 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12412,13 +12453,13 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>492</v>
+        <v>166</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>493</v>
+        <v>167</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12457,43 +12498,43 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC85" t="s" s="2">
+      <c r="AG85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12504,14 +12545,12 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12520,7 +12559,7 @@
         <v>92</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12532,13 +12571,13 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>497</v>
+        <v>138</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12577,19 +12616,19 @@
         <v>82</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12624,18 +12663,20 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="D87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>92</v>
@@ -12650,13 +12691,13 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>161</v>
+        <v>508</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>162</v>
+        <v>509</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>163</v>
+        <v>510</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12707,19 +12748,19 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12731,7 +12772,7 @@
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12742,10 +12783,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12756,7 +12797,7 @@
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -12768,13 +12809,13 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>492</v>
+        <v>166</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>493</v>
+        <v>167</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12813,43 +12854,43 @@
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC88" t="s" s="2">
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12860,10 +12901,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12871,10 +12912,10 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -12886,24 +12927,22 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>82</v>
@@ -12933,31 +12972,31 @@
         <v>82</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>540</v>
+        <v>175</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -12969,7 +13008,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -12980,10 +13019,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12991,7 +13030,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>92</v>
@@ -13006,25 +13045,27 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>183</v>
+        <v>106</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>82</v>
@@ -13039,11 +13080,13 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y90" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z90" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13061,10 +13104,10 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>92</v>
@@ -13073,7 +13116,7 @@
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13096,10 +13139,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>500</v>
+        <v>553</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13119,20 +13162,18 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>501</v>
+        <v>554</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13142,7 +13183,7 @@
         <v>82</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>82</v>
+        <v>588</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>82</v>
@@ -13157,13 +13198,11 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>82</v>
+        <v>557</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13181,7 +13220,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>504</v>
+        <v>558</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13190,7 +13229,7 @@
         <v>92</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>104</v>
@@ -13216,10 +13255,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13242,16 +13281,16 @@
         <v>93</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13277,13 +13316,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13301,7 +13340,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13310,7 +13349,7 @@
         <v>92</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>104</v>
@@ -13336,10 +13375,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13362,16 +13401,16 @@
         <v>93</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13397,13 +13436,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13421,7 +13460,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13445,7 +13484,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13456,10 +13495,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13482,16 +13521,16 @@
         <v>93</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13541,7 +13580,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13565,7 +13604,7 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13576,23 +13615,21 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>583</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13601,19 +13638,19 @@
         <v>82</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>525</v>
+        <v>165</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>584</v>
+        <v>530</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>484</v>
+        <v>531</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>485</v>
+        <v>532</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13663,13 +13700,13 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>480</v>
+        <v>533</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
@@ -13678,16 +13715,16 @@
         <v>104</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>583</v>
+        <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>487</v>
+        <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>488</v>
+        <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>489</v>
+        <v>135</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13698,21 +13735,23 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C96" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>594</v>
+      </c>
       <c r="D96" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13724,15 +13763,17 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>161</v>
+        <v>536</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>162</v>
+        <v>595</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13781,31 +13822,31 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>164</v>
+        <v>491</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>82</v>
+        <v>594</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>165</v>
+        <v>500</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -13816,10 +13857,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13827,10 +13868,10 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
@@ -13842,13 +13883,13 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>492</v>
+        <v>166</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>493</v>
+        <v>167</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13887,43 +13928,43 @@
         <v>82</v>
       </c>
       <c r="AB97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF97" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC97" t="s" s="2">
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -13934,14 +13975,12 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>82</v>
       </c>
@@ -13950,7 +13989,7 @@
         <v>92</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
@@ -13962,13 +14001,13 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>497</v>
+        <v>138</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14007,19 +14046,19 @@
         <v>82</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14054,18 +14093,20 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="C99" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="D99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>92</v>
@@ -14080,13 +14121,13 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>161</v>
+        <v>508</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>162</v>
+        <v>509</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>163</v>
+        <v>510</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14137,19 +14178,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14161,7 +14202,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14172,10 +14213,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14186,7 +14227,7 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
@@ -14198,13 +14239,13 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>492</v>
+        <v>166</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>493</v>
+        <v>167</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14243,43 +14284,43 @@
         <v>82</v>
       </c>
       <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC100" t="s" s="2">
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14290,10 +14331,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14301,10 +14342,10 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14316,24 +14357,22 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14363,31 +14402,31 @@
         <v>82</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>540</v>
+        <v>175</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
@@ -14399,7 +14438,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14410,10 +14449,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14421,7 +14460,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>92</v>
@@ -14436,25 +14475,27 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>183</v>
+        <v>106</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>82</v>
@@ -14469,11 +14510,13 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y102" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z102" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14491,10 +14534,10 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>92</v>
@@ -14503,7 +14546,7 @@
         <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>82</v>
@@ -14526,10 +14569,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>500</v>
+        <v>553</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14549,20 +14592,18 @@
         <v>82</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>501</v>
+        <v>554</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14572,7 +14613,7 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>82</v>
+        <v>603</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>82</v>
@@ -14587,13 +14628,11 @@
         <v>82</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>82</v>
+        <v>557</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14611,7 +14650,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>504</v>
+        <v>558</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14620,7 +14659,7 @@
         <v>92</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>104</v>
@@ -14646,10 +14685,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14672,16 +14711,16 @@
         <v>93</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14707,13 +14746,13 @@
         <v>82</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14731,7 +14770,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14740,7 +14779,7 @@
         <v>92</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>104</v>
@@ -14766,10 +14805,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14792,16 +14831,16 @@
         <v>93</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14827,13 +14866,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -14851,7 +14890,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14875,7 +14914,7 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -14886,10 +14925,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14912,16 +14951,16 @@
         <v>93</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14971,7 +15010,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14995,7 +15034,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15006,10 +15045,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>597</v>
+        <v>607</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>597</v>
+        <v>529</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15020,7 +15059,7 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>82</v>
@@ -15032,16 +15071,16 @@
         <v>93</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>598</v>
+        <v>165</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>599</v>
+        <v>530</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>600</v>
+        <v>531</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>601</v>
+        <v>532</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15091,13 +15130,13 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>597</v>
+        <v>533</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>82</v>
@@ -15112,10 +15151,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>602</v>
+        <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>603</v>
+        <v>135</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15126,14 +15165,14 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>605</v>
+        <v>82</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15152,20 +15191,18 @@
         <v>93</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>183</v>
+        <v>609</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>609</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15189,13 +15226,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>611</v>
+        <v>82</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15213,7 +15250,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15234,28 +15271,28 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>613</v>
+        <v>82</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>82</v>
+        <v>616</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -15271,19 +15308,23 @@
         <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>615</v>
+        <v>189</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>50</v>
+        <v>617</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+        <v>618</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>620</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15307,13 +15348,13 @@
         <v>82</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>82</v>
+        <v>621</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>82</v>
+        <v>622</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15331,7 +15372,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15349,27 +15390,27 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>617</v>
+        <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>332</v>
+        <v>613</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15380,7 +15421,7 @@
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15389,16 +15430,16 @@
         <v>82</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>161</v>
+        <v>626</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>621</v>
+        <v>50</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15449,13 +15490,13 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
@@ -15467,27 +15508,27 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>82</v>
+        <v>628</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>82</v>
+        <v>630</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15498,7 +15539,7 @@
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>82</v>
@@ -15507,20 +15548,18 @@
         <v>82</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>625</v>
+        <v>165</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>628</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15569,13 +15608,13 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
@@ -15587,18 +15626,138 @@
         <v>82</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>629</v>
+        <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AM112" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="AN111" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP111" t="s" s="2">
+      <c r="AN112" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP112" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:13:13+00:00</t>
+    <t>2026-06-15T13:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T13:25:13+00:00</t>
+    <t>2026-06-16T07:36:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T07:36:31+00:00</t>
+    <t>2026-06-16T07:55:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T07:55:16+00:00</t>
+    <t>2026-06-16T08:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:15:37+00:00</t>
+    <t>2026-06-17T09:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:17:48+00:00</t>
+    <t>2026-06-17T09:36:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:36:47+00:00</t>
+    <t>2026-06-19T10:27:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:32:11+00:00</t>
+    <t>2026-06-24T08:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -501,9 +501,6 @@
     <t>open</t>
   </si>
   <si>
-    <t>idDemandeOrientation</t>
-  </si>
-  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -711,6 +708,9 @@
   </si>
   <si>
     <t>ServiceRequest.identifier:idDemandeOrientation</t>
+  </si>
+  <si>
+    <t>idDemandeOrientation</t>
   </si>
   <si>
     <t>ServiceRequest.identifier:idDemandeOrientation.id</t>
@@ -3685,30 +3685,30 @@
         <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3731,13 +3731,13 @@
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3788,31 +3788,31 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3823,10 +3823,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3855,7 +3855,7 @@
         <v>139</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N13" t="s" s="2">
         <v>141</v>
@@ -3896,10 +3896,10 @@
         <v>82</v>
       </c>
       <c r="AB13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC13" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>82</v>
@@ -3908,7 +3908,7 @@
         <v>155</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3932,7 +3932,7 @@
         <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3943,10 +3943,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3972,16 +3972,16 @@
         <v>112</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -4006,31 +4006,31 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4054,7 +4054,7 @@
         <v>135</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>82</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4091,19 +4091,19 @@
         <v>93</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4128,29 +4128,29 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4171,10 +4171,10 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>82</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4214,16 +4214,16 @@
         <v>106</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4236,43 +4236,43 @@
         <v>82</v>
       </c>
       <c r="T16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4293,10 +4293,10 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4333,16 +4333,16 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4356,43 +4356,43 @@
         <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4413,10 +4413,10 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -4427,10 +4427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4453,13 +4453,13 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4510,7 +4510,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4531,10 +4531,10 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4545,10 +4545,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4571,16 +4571,16 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4630,7 +4630,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4651,10 +4651,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4665,13 +4665,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>149</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>82</v>
@@ -4767,22 +4767,22 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>161</v>
       </c>
     </row>
     <row r="21">
@@ -4790,7 +4790,7 @@
         <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4813,13 +4813,13 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4870,31 +4870,31 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4908,7 +4908,7 @@
         <v>226</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4937,7 +4937,7 @@
         <v>139</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>141</v>
@@ -4978,10 +4978,10 @@
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC22" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>82</v>
@@ -4990,7 +4990,7 @@
         <v>155</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5014,7 +5014,7 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -5028,7 +5028,7 @@
         <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5054,16 +5054,16 @@
         <v>112</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -5088,31 +5088,31 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y23" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y23" t="s" s="2">
+      <c r="Z23" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Z23" t="s" s="2">
+      <c r="AA23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5136,7 +5136,7 @@
         <v>135</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5150,7 +5150,7 @@
         <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5173,19 +5173,19 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5210,29 +5210,29 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5253,10 +5253,10 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5270,7 +5270,7 @@
         <v>230</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5299,13 +5299,13 @@
         <v>231</v>
       </c>
       <c r="M25" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5318,43 +5318,43 @@
         <v>82</v>
       </c>
       <c r="T25" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5375,10 +5375,10 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5392,7 +5392,7 @@
         <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5415,16 +5415,16 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5438,43 +5438,43 @@
         <v>82</v>
       </c>
       <c r="T26" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5495,10 +5495,10 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5512,7 +5512,7 @@
         <v>233</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5535,13 +5535,13 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5592,7 +5592,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5613,10 +5613,10 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5630,7 +5630,7 @@
         <v>234</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5653,16 +5653,16 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5712,7 +5712,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5733,10 +5733,10 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -6406,7 +6406,7 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y34" t="s" s="2">
         <v>277</v>
@@ -6526,7 +6526,7 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y35" t="s" s="2">
         <v>288</v>
@@ -6611,7 +6611,7 @@
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>294</v>
@@ -6648,7 +6648,7 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
@@ -6766,7 +6766,7 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y37" t="s" s="2">
         <v>306</v>
@@ -6975,7 +6975,7 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>323</v>
@@ -7010,7 +7010,7 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
@@ -7093,7 +7093,7 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>335</v>
@@ -7687,7 +7687,7 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>372</v>
@@ -7805,13 +7805,13 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7862,31 +7862,31 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7929,7 +7929,7 @@
         <v>139</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>141</v>
@@ -7970,10 +7970,10 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC47" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
@@ -7982,7 +7982,7 @@
         <v>155</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8006,7 +8006,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8641,7 +8641,7 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>437</v>
@@ -8881,7 +8881,7 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>456</v>
@@ -9117,7 +9117,7 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>466</v>
@@ -9593,13 +9593,13 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9650,31 +9650,31 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9756,10 +9756,10 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC62" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
@@ -9768,7 +9768,7 @@
         <v>155</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9888,7 +9888,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9949,7 +9949,7 @@
         <v>93</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>511</v>
@@ -10272,7 +10272,7 @@
         <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10309,7 +10309,7 @@
         <v>93</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>530</v>
@@ -10551,13 +10551,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10608,31 +10608,31 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10714,10 +10714,10 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC70" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
@@ -10726,7 +10726,7 @@
         <v>155</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10846,7 +10846,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10907,13 +10907,13 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10964,31 +10964,31 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11070,10 +11070,10 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC73" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
@@ -11082,7 +11082,7 @@
         <v>155</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11263,7 +11263,7 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>554</v>
@@ -11296,7 +11296,7 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
@@ -11379,7 +11379,7 @@
         <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>511</v>
@@ -11702,7 +11702,7 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11739,7 +11739,7 @@
         <v>93</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>530</v>
@@ -11981,13 +11981,13 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12038,31 +12038,31 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12144,10 +12144,10 @@
         <v>82</v>
       </c>
       <c r="AB82" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC82" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>82</v>
@@ -12156,7 +12156,7 @@
         <v>155</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12276,7 +12276,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12337,13 +12337,13 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12394,31 +12394,31 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12500,10 +12500,10 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC85" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
@@ -12512,7 +12512,7 @@
         <v>155</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12693,7 +12693,7 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>554</v>
@@ -12726,7 +12726,7 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
@@ -12809,7 +12809,7 @@
         <v>93</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>511</v>
@@ -13132,7 +13132,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13169,7 +13169,7 @@
         <v>93</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L91" t="s" s="2">
         <v>530</v>
@@ -13411,13 +13411,13 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13468,31 +13468,31 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13574,10 +13574,10 @@
         <v>82</v>
       </c>
       <c r="AB94" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC94" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>82</v>
@@ -13586,7 +13586,7 @@
         <v>155</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13706,7 +13706,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13767,13 +13767,13 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13824,31 +13824,31 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -13930,10 +13930,10 @@
         <v>82</v>
       </c>
       <c r="AB97" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC97" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>82</v>
@@ -13942,7 +13942,7 @@
         <v>155</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14123,7 +14123,7 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L99" t="s" s="2">
         <v>554</v>
@@ -14156,7 +14156,7 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
@@ -14239,7 +14239,7 @@
         <v>93</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>511</v>
@@ -14562,7 +14562,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14599,7 +14599,7 @@
         <v>93</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>530</v>
@@ -14841,13 +14841,13 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14898,31 +14898,31 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15004,10 +15004,10 @@
         <v>82</v>
       </c>
       <c r="AB106" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC106" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>82</v>
@@ -15016,7 +15016,7 @@
         <v>155</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15136,7 +15136,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15197,13 +15197,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15254,31 +15254,31 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15360,10 +15360,10 @@
         <v>82</v>
       </c>
       <c r="AB109" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC109" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>82</v>
@@ -15372,7 +15372,7 @@
         <v>155</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15553,7 +15553,7 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L111" t="s" s="2">
         <v>554</v>
@@ -15586,7 +15586,7 @@
         <v>82</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
@@ -15669,7 +15669,7 @@
         <v>93</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>511</v>
@@ -15992,7 +15992,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16029,7 +16029,7 @@
         <v>93</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L115" t="s" s="2">
         <v>530</v>
@@ -16269,7 +16269,7 @@
         <v>93</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L117" t="s" s="2">
         <v>617</v>
@@ -16509,7 +16509,7 @@
         <v>93</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L119" t="s" s="2">
         <v>632</v>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T08:54:25+00:00</t>
+    <t>2026-06-24T09:36:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T09:36:36+00:00</t>
+    <t>2026-06-24T12:11:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:11:25+00:00</t>
+    <t>2026-06-24T12:16:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:16:25+00:00</t>
+    <t>2026-06-25T08:27:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T08:27:57+00:00</t>
+    <t>2026-06-25T09:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T09:12:27+00:00</t>
+    <t>2026-06-25T09:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T09:43:13+00:00</t>
+    <t>2026-06-25T10:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T10:03:25+00:00</t>
+    <t>2026-06-25T10:20:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T10:20:08+00:00</t>
+    <t>2026-06-25T14:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-service-request-demande-orientation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0-ballot</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:41:02+00:00</t>
+    <t>2026-06-30T07:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
